--- a/ig/DM-37/CodeSystem-TRE-R49-DiplomeEtudeSpecialisee.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R49-DiplomeEtudeSpecialisee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,42 +499,63 @@
     <t>DES Pharmacie hospitalière</t>
   </si>
   <si>
+    <t>DES de pharmacie hospitalière (nouveau régime) sans mention de l'option. Suite au décret n° 2019-1022 du 4 octobre 2019 portant modification du troisième cycle long des études pharmaceutiques, le DES de pharmacie hospitalière remplace le DES de pharmacie à compter de la rentrée universitaire 2019-2020 (premiers diplômés en 2024 pour les options PHG et DSPS, et 2025 pour l'option RPH). Si l'option n'est pas connue, le code du DES de pharmacie hospitalière est DSP06, sinon le code est DSP10, DSP11 ou DSP12.</t>
+  </si>
+  <si>
     <t>DSP07</t>
   </si>
   <si>
     <t>DES Pharmacie hospitalière (PHPR)</t>
   </si>
   <si>
+    <t>DES de pharmacie (ancien régime) option pharmacie hospitalière - pratique et recherche (PH-PR).</t>
+  </si>
+  <si>
     <t>DSP08</t>
   </si>
   <si>
     <t>DES Pharmacie industrielle et biomédicale (PIBM)</t>
   </si>
   <si>
+    <t>DES de pharmacie (ancien régime) option pharmacie industrielle et biomédicale (PIBM).</t>
+  </si>
+  <si>
     <t>DSP09</t>
   </si>
   <si>
     <t>DES Pharmacie</t>
   </si>
   <si>
+    <t>DES de pharmacie (ancien régime) sans mention de l'option. Suite au décret n° 2019-1022 du 4 octobre 2019 portant modification du troisième cycle long des études pharmaceutiques, le DES de pharmacie hospitalière remplace le DES de pharmacie à compter de la rentrée universitaire 2019-2020 (derniers diplômés du DES de pharmacie en 2023). Si l'option n'est pas connue, le code du DES de pharmacie est DSP09, sinon le code est DSP07 ou DSP08.</t>
+  </si>
+  <si>
     <t>DSP10</t>
   </si>
   <si>
     <t>DES Pharmacie hospitalière générale (PHG)</t>
   </si>
   <si>
+    <t>DES de pharmacie hospitalière (nouveau régime) option Pharmacie Hospitalière Générale (PHG).</t>
+  </si>
+  <si>
     <t>DSP11</t>
   </si>
   <si>
     <t>DES Pharmacie hospitalière développement-sécurisation des produits santé (DSPS)</t>
   </si>
   <si>
+    <t>DES de pharmacie hospitalière (nouveau régime) option Développement et sécurisation des produits de santé (DSPS).</t>
+  </si>
+  <si>
     <t>DSP12</t>
   </si>
   <si>
     <t>DES Pharmacie hospitalière radiopharmacie (RPH)</t>
   </si>
   <si>
+    <t>DES de pharmacie hospitalière (nouveau régime) option Radiopharmacie (RPH).</t>
+  </si>
+  <si>
     <t>DSM52</t>
   </si>
   <si>
@@ -815,6 +836,9 @@
   </si>
   <si>
     <t>DES Biologie méd opt bactério, virologie, hygiène</t>
+  </si>
+  <si>
+    <t>Bulletin officiel n°19 du 11 mai 2006 (DES antérieur à la réforme de 2017)</t>
   </si>
   <si>
     <t>DSM99</t>
@@ -1923,89 +1947,103 @@
       <c r="C57" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>161</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="D58" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="D59" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>167</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="D60" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>170</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="D61" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>173</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="D62" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>176</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="D63" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>179</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -2014,10 +2052,10 @@
         <v>49</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -2026,10 +2064,10 @@
         <v>49</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -2038,10 +2076,10 @@
         <v>49</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -2050,10 +2088,10 @@
         <v>49</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -2062,10 +2100,10 @@
         <v>49</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -2074,10 +2112,10 @@
         <v>49</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -2086,10 +2124,10 @@
         <v>49</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -2098,10 +2136,10 @@
         <v>49</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -2110,10 +2148,10 @@
         <v>49</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -2122,10 +2160,10 @@
         <v>49</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -2134,10 +2172,10 @@
         <v>49</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -2146,10 +2184,10 @@
         <v>49</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -2158,10 +2196,10 @@
         <v>49</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -2170,10 +2208,10 @@
         <v>49</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -2182,10 +2220,10 @@
         <v>49</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -2194,10 +2232,10 @@
         <v>49</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -2206,10 +2244,10 @@
         <v>49</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -2218,10 +2256,10 @@
         <v>49</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -2230,10 +2268,10 @@
         <v>49</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -2242,10 +2280,10 @@
         <v>49</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -2254,10 +2292,10 @@
         <v>49</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -2266,10 +2304,10 @@
         <v>49</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -2278,10 +2316,10 @@
         <v>49</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -2290,10 +2328,10 @@
         <v>49</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -2302,10 +2340,10 @@
         <v>49</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -2314,10 +2352,10 @@
         <v>49</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -2326,10 +2364,10 @@
         <v>49</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -2338,10 +2376,10 @@
         <v>49</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -2350,10 +2388,10 @@
         <v>49</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -2362,10 +2400,10 @@
         <v>49</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -2374,10 +2412,10 @@
         <v>49</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -2386,10 +2424,10 @@
         <v>49</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -2398,10 +2436,10 @@
         <v>49</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -2410,10 +2448,10 @@
         <v>49</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -2422,10 +2460,10 @@
         <v>49</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -2434,10 +2472,10 @@
         <v>49</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D100" s="2"/>
     </row>
@@ -2446,10 +2484,10 @@
         <v>49</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -2458,10 +2496,10 @@
         <v>49</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -2470,10 +2508,10 @@
         <v>49</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -2482,10 +2520,10 @@
         <v>49</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -2494,10 +2532,10 @@
         <v>49</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -2506,10 +2544,10 @@
         <v>49</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -2518,10 +2556,10 @@
         <v>49</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -2530,10 +2568,10 @@
         <v>49</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -2542,10 +2580,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -2554,108 +2592,126 @@
         <v>49</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="D110" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="D111" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="D112" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="D113" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C114" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="D114" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="D115" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="D116" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="D117" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="D118" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>274</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
